--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\cruzamento_medias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2732985A-C883-4428-A97F-0D4BB88E289C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921D37FA-DA7D-4075-A12A-87DFB75548EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14055" yWindow="825" windowWidth="12585" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ticker</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>SPCX34</t>
+  </si>
+  <si>
+    <t>IVVB11</t>
   </si>
 </sst>
 </file>
@@ -392,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -463,6 +466,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
